--- a/public_html/assets/templates/clients-import-template.xlsx
+++ b/public_html/assets/templates/clients-import-template.xlsx
@@ -1,67 +1,62 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="500" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Hoja1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
-  <si>
-    <t xml:space="preserve">commercial_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">legal_name </t>
-  </si>
-  <si>
-    <t xml:space="preserve">cif </t>
-  </si>
-  <si>
-    <t xml:space="preserve">address </t>
-  </si>
-  <si>
-    <t xml:space="preserve">postal_code </t>
-  </si>
-  <si>
-    <t xml:space="preserve">city </t>
-  </si>
-  <si>
-    <t xml:space="preserve">province </t>
-  </si>
-  <si>
-    <t xml:space="preserve">country </t>
-  </si>
-  <si>
-    <t xml:space="preserve">website </t>
-  </si>
-  <si>
-    <t xml:space="preserve">notes </t>
-  </si>
-  <si>
-    <t xml:space="preserve">sector </t>
-  </si>
-  <si>
-    <t xml:space="preserve">tags </t>
-  </si>
-  <si>
-    <t xml:space="preserve">contact </t>
-  </si>
-  <si>
-    <t xml:space="preserve">custom_fields.iban</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="26">
+  <si>
+    <t>commercial_name</t>
+  </si>
+  <si>
+    <t>legal_name</t>
+  </si>
+  <si>
+    <t>cif</t>
+  </si>
+  <si>
+    <t>address</t>
+  </si>
+  <si>
+    <t>postal_code</t>
+  </si>
+  <si>
+    <t>city</t>
+  </si>
+  <si>
+    <t>province</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>website</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>sector</t>
+  </si>
+  <si>
+    <t>tags</t>
+  </si>
+  <si>
+    <t>contact</t>
+  </si>
+  <si>
+    <t>iban</t>
   </si>
   <si>
     <t xml:space="preserve">Acme Solutions </t>
@@ -97,42 +92,32 @@
     <t xml:space="preserve">John Smith </t>
   </si>
   <si>
-    <t xml:space="preserve">ES63 0021 0245 0440 0137 3224</t>
+    <t>ES63 0021 0245 0440 0137 3224</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="@"/>
-  </numFmts>
-  <fonts count="5">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -144,7 +129,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -152,65 +137,38 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="3">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="true">
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf xfId="0" fontId="0" numFmtId="49" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="true">
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf xfId="0" fontId="1" numFmtId="49" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="LibreOffice">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
@@ -245,86 +203,205 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="DejaVu Sans"/>
+        <a:cs typeface="DejaVu Sans"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="DejaVu Sans"/>
+        <a:cs typeface="DejaVu Sans"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter/>
         </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter/>
         </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="11.53515625" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14.74"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="21.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="19.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="29.35"/>
+    <col min="1" max="1" width="16.27" customWidth="true" style="0"/>
+    <col min="2" max="2" width="15.85" customWidth="true" style="0"/>
+    <col min="4" max="4" width="14.74" customWidth="true" style="0"/>
+    <col min="9" max="9" width="21.43" customWidth="true" style="0"/>
+    <col min="10" max="10" width="19.33" customWidth="true" style="0"/>
+    <col min="14" max="14" width="29.35" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:14" customHeight="1" ht="12.8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -368,7 +445,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:14" customHeight="1" ht="12.8">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -381,7 +458,7 @@
       <c r="D2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="2">
         <v>28001</v>
       </c>
       <c r="F2" s="2" t="s">
@@ -413,10 +490,10 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <printOptions gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.0527777777778" bottom="1.0527777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="1" pageOrder="downThenOver"/>
+  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
     <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Página &amp;P</oddFooter>
   </headerFooter>
